--- a/Result/profitability/8067.xlsx
+++ b/Result/profitability/8067.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         <v>-0.16</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.2625</v>
+        <v>-0.15375</v>
       </c>
       <c r="N2" t="n">
-        <v>39.26125</v>
+        <v>40.20375</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.79</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.33375</v>
+        <v>-0.1875</v>
       </c>
       <c r="N3" t="n">
-        <v>33.23875</v>
+        <v>35.07875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.19875</v>
+        <v>-0.07875000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>28.75375</v>
+        <v>30.69625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.47</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.10125</v>
+        <v>0.04124999999999997</v>
       </c>
       <c r="N5" t="n">
-        <v>24.865</v>
+        <v>27.47375</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.12</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.02500000000000003</v>
+        <v>-0.04625000000000002</v>
       </c>
       <c r="N6" t="n">
-        <v>21.4125</v>
+        <v>23.0075</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.16</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1075</v>
+        <v>0.04874999999999997</v>
       </c>
       <c r="N7" t="n">
-        <v>17.5575</v>
+        <v>19.54125</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,13 +1391,13 @@
         <v>0.04</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.02750000000000002</v>
+        <v>0.13125</v>
       </c>
       <c r="N8" t="n">
-        <v>13.1825</v>
+        <v>14.03875</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8067</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>24</v>
+      </c>
+      <c r="D75" t="n">
+        <v>10</v>
+      </c>
+      <c r="E75" t="n">
+        <v>14</v>
+      </c>
+      <c r="F75" t="n">
+        <v>57.29</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-13.33%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>17</v>
+      </c>
+      <c r="J75" t="n">
+        <v>14</v>
+      </c>
+      <c r="K75" t="n">
+        <v>14</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.16125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>45.52125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-2.048387096774194</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>6.850000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1358049167327517</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-2.326530612244898</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>20.87</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.573036792970895</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
